--- a/PERFIL_PAM_VERDE_BEIRA_C3_2026.xlsx
+++ b/PERFIL_PAM_VERDE_BEIRA_C3_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DionisioMahumane\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/Pam_Verde/2026/Baseline_Endline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5040D066-AE66-F545-AC8C-766D23DB4958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{5040D066-AE66-F545-AC8C-766D23DB4958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DE1BE19-401E-40C5-AB3F-ACF032A36325}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -655,7 +655,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -972,18 +972,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.0078125" customWidth="1"/>
-    <col min="2" max="2" width="32.1484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="16.0078125" customWidth="1"/>
-    <col min="7" max="7" width="19.37109375" customWidth="1"/>
-    <col min="8" max="8" width="50.71484375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.484375" customWidth="1"/>
-    <col min="10" max="10" width="28.65234375" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1169,13 +1169,13 @@
         <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>185</v>
       </c>
       <c r="J6" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>64</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>72</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>78</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>83</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>91</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>93</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>95</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>100</v>
       </c>
@@ -1649,13 +1649,13 @@
         <v>13</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>185</v>
       </c>
       <c r="J21" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>107</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>117</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>121</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>123</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>128</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>133</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>137</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>142</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>147</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>152</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>155</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>160</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>165</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>167</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>173</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>178</v>
       </c>
@@ -2525,13 +2525,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3A38ED6-98BC-4E30-A47E-B9EADBC2F7FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77C68ADF-A96E-4EDC-97D4-EE1BC02684C0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15098CC0-5FCE-4BE0-8984-72AC220AC74D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15098CC0-5FCE-4BE0-8984-72AC220AC74D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91B60EC3-BD84-4E67-9739-9EA7921CE3DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91B60EC3-BD84-4E67-9739-9EA7921CE3DB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>